--- a/astro-site/public/dl/restaurant-schedule-templates/03-labor-cost-calculator.xlsx
+++ b/astro-site/public/dl/restaurant-schedule-templates/03-labor-cost-calculator.xlsx
@@ -796,14 +796,14 @@
     <row r="8">
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>▸ The "Cost per hour worked" column is the number to carry to the hourly rate of file 02 (Overtime Tracker &amp; Time Log (FLSA 40-Hour Week)): it is the real employer cost, not the plain hourly wage. It divides by the WEEKS ACTUALLY WORKED (green cell F2, 50 by default; UK about 46.4), not by the 52 of the calendar: paid time off and holidays are paid but not worked, so with 52 the cost per hour comes out about 4% short.</t>
+          <t>▸ The "Cost per hour worked" column is the number to carry to the hourly rate of file 02 "Overtime Tracker &amp; Time Log": it is the real employer cost, not the plain hourly wage. It divides by the WEEKS ACTUALLY WORKED (green cell F2, 50 by default; UK about 46.4), not by the 52 of the calendar: paid time off and holidays are paid but not worked, so with 52 the cost per hour comes out about 4% short.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>▸ In "Labor Cost Ratio", the month's cost is NOT just payroll: there are three green cells for the month's overtime (the total of the cost column in file 02 (Overtime Tracker &amp; Time Log (FLSA 40-Hour Week))), agency / temp staff and other staff costs. Without them the ratio comes out below the real one and the traffic light approves too easily.</t>
+          <t>▸ In "Labor Cost Ratio", the month's cost is NOT just payroll: there are three green cells for the month's overtime (the total of the cost column in file 02 "Overtime Tracker &amp; Time Log"), agency / temp staff and other staff costs. Without them the ratio comes out below the real one and the traffic light approves too easily.</t>
         </is>
       </c>
     </row>
@@ -1804,11 +1804,11 @@
     <mergeCell ref="A3:I3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="C2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2 · employer_tax_rate" prompt="Adjust to your state, insurer and unemployment rate. Estimate: about 10% = FICA 7.65% + FUTA/SUTA + workers' comp. UK: employer NI 15% above 5,000 a year + about 3% pension."/>
-    <dataValidation sqref="F2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Weeks worked per year" error="Type a number greater than zero." promptTitle="kitgp-v2b · Weeks per year" prompt="52 weeks MINUS paid time off and holidays (paid, not worked): about 50 with two weeks of PTO (UK: 46.4). It divides &quot;Cost per hour worked&quot;: with 52 that cost comes out about 4% short, and you carry it to the rate in file 02." type="decimal" errorStyle="stop" operator="greaterThan">
+    <dataValidation sqref="C2" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Employer taxes &amp; insurance" prompt="Adjust to your state, insurer and unemployment rate. Estimate: about 10% = FICA 7.65% + FUTA/SUTA + workers' comp. UK: employer NI 15% above 5,000 a year + about 3% pension."/>
+    <dataValidation sqref="F2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Weeks worked per year" error="Type a number greater than zero." promptTitle="Weeks worked per year" prompt="52 weeks MINUS paid time off and holidays (paid, not worked): about 50 with two weeks of PTO (UK: 46.4). It divides &quot;Cost per hour worked&quot;: with 52 that cost comes out about 4% short, and you carry it to the rate in file 02." type="decimal" errorStyle="stop" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid pay periods" error="52, 26, 24 or 12. Column E converts the gross pay per period to a monthly figure." promptTitle="kitgp-v2b · Invalid pay periods" prompt="26 = every two weeks (biweekly, the US norm) · 52 = weekly · 24 = twice a month · 12 = monthly. Column E converts to the REAL monthly cost: gross per period × periods per year ÷ 12." type="list" errorStyle="stop">
+    <dataValidation sqref="D5:D34" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid pay periods" error="52, 26, 24 or 12. Column E converts the gross pay per period to a monthly figure." promptTitle="Pay periods per year" prompt="26 = every two weeks (biweekly, the US norm) · 52 = weekly · 24 = twice a month · 12 = monthly. Column E converts to the REAL monthly cost: gross per period × periods per year ÷ 12." type="list" errorStyle="stop">
       <formula1>"52,26,24,12"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2271,16 +2271,16 @@
     <mergeCell ref="A14:E14"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid concept" error="Pick one of the ten concepts in the reference table below." promptTitle="kitgp-v2b · Invalid concept" prompt="The two traffic-light thresholds come from here by VLOOKUP on the table of this sheet. Same ten concepts and thresholds as the BONUS-02 calculator: the two files cannot give different verdicts on the same ratio. If blank, the generic 30% / 35% applies." type="list" errorStyle="stop">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid concept" error="Pick one of the ten concepts in the reference table below." promptTitle="Restaurant concept" prompt="The two traffic-light thresholds come from here by VLOOKUP on the table of this sheet. Same ten concepts and thresholds as the BONUS-02 calculator: the two files cannot give different verdicts on the same ratio. If blank, the generic 30% / 35% applies." type="list" errorStyle="stop">
       <formula1>"Fast casual / QSR,Casual dining,Fine dining,Catering &amp; events,Café / brunch,Bar / cocktail bar,Pizzeria,Ghost kitchen / delivery,Hotel restaurant,Ice cream shop / bakery"</formula1>
     </dataValidation>
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Overtime for the month" error="Type a number greater than zero." promptTitle="kitgp-v2b · Monthly overtime" prompt="Copy it from &quot;Monthly OT Summary&quot;!G37 in file 02 (Overtime Tracker &amp; Time Log (FLSA 40-Hour Week)) (the total of the &quot;Overtime cost&quot; column). The kit calculates it, and leaving it out makes the ratio come out short." type="decimal" errorStyle="stop" operator="greaterThan">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Overtime for the month" error="Type a number greater than zero." promptTitle="Monthly overtime" prompt="Copy it from &quot;Monthly OT Summary&quot;!G37 in file 02 &quot;Overtime Tracker &amp; Time Log&quot; (the total of its &quot;Overtime cost&quot; column; add up the copies that fall in the month). Leaving it out makes the ratio come out short." type="decimal" errorStyle="stop" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Agency / temp staff" error="Type a number greater than zero." promptTitle="kitgp-v2b · Agency / temp staff" prompt="Weekend extras, temp agency, peak-day backup staff (the kind BONUS-02 recommends hiring). It is labor cost even if it is not on your payroll." type="decimal" errorStyle="stop" operator="greaterThan">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Agency / temp staff" error="Type a number greater than zero." promptTitle="Agency / temp staff" prompt="Weekend extras, temp agency, peak-day backup staff (the kind BONUS-02 recommends hiring). It is labor cost even if it is not on your payroll." type="decimal" errorStyle="stop" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Other staff costs" error="Type a number greater than zero." promptTitle="kitgp-v2b · Other staff costs" prompt="Per diems, required training, uniforms, transport, staff meals… anything your accounting charges to labor that does not come from payroll." type="decimal" errorStyle="stop" operator="greaterThan">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Other staff costs" error="Type a number greater than zero." promptTitle="Other staff costs" prompt="Per diems, required training, uniforms, transport, staff meals… anything your accounting charges to labor that does not come from payroll." type="decimal" errorStyle="stop" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -2601,7 +2601,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid services per day" error="Pick 1, 2 or 3." promptTitle="kitgp-v2b · Invalid services/day" prompt="One (lunch only or dinner only), two (lunch and dinner) or three (breakfast, lunch and dinner). It splits the day's covers across services: eighty covers in two services are forty per service, and the team is sized for those forty." type="list" errorStyle="stop">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid services per day" error="Pick 1, 2 or 3." promptTitle="Services per day" prompt="One (lunch only or dinner only), two (lunch and dinner) or three (breakfast, lunch and dinner). It splits the day's covers across services: eighty covers in two services are forty per service, and the team is sized for those forty." type="list" errorStyle="stop">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
   </dataValidations>
